--- a/pontuacao_final.xlsx
+++ b/pontuacao_final.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,31 +431,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DANILO</t>
+          <t>Danilo</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>192</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JOHN DOE</t>
+          <t>Jogador</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>JOGADOR</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/pontuacao_final.xlsx
+++ b/pontuacao_final.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
